--- a/languages/de/output/import/德语A2.xlsx
+++ b/languages/de/output/import/德语A2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="词汇表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="词汇表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/languages/de/output/import/德语A2.xlsx
+++ b/languages/de/output/import/德语A2.xlsx
@@ -36435,7 +36435,7 @@
       </c>
       <c r="B1126" s="1" t="inlineStr">
         <is>
-          <t>[t͡svɛk] 目的〈n.m.〉</t>
+          <t>[t͡svɛk] 目的；意图；宗旨〈n.m.〉</t>
         </is>
       </c>
       <c r="C1126" s="1" t="inlineStr">
@@ -36445,7 +36445,7 @@
       </c>
       <c r="D1126" s="1" t="inlineStr">
         <is>
-          <t>目的</t>
+          <t>目的；意图；宗旨</t>
         </is>
       </c>
       <c r="E1126" s="1" t="inlineStr">

--- a/languages/de/output/import/德语A2.xlsx
+++ b/languages/de/output/import/德语A2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="词汇表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="词汇表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>[ɔʁdnʊnk] 秩序；正常（没问题）〈n.f.〉</t>
+          <t>[ɔʁdnʊŋ] 秩序；正常（没问题）〈n.f.〉</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>ɔʁdnʊnk</t>
+          <t>ɔʁdnʊŋ</t>
         </is>
       </c>
       <c r="D21" s="1" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>[hiːn] （方向）过去〈adv.〉</t>
+          <t>[hiːn] 去；向那边；往那边〈adv.〉〈adv.〉</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
-          <t>（方向）过去</t>
+          <t>去；向那边；往那边〈adv.〉</t>
         </is>
       </c>
       <c r="E25" s="1" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>[ɛçt] 真的（口语）〈adj.〉</t>
+          <t>[ɛçt] 真正的；真实的；纯正的〈adj.〉</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
-          <t>真的（口语）</t>
+          <t>真正的；真实的；纯正的</t>
         </is>
       </c>
       <c r="E48" s="1" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>[aːnʊnk] 概念；线索〈n.f.〉</t>
+          <t>[aːnʊnk] 预感；概念；大致了解〈f.〉〈n.f.〉</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="D58" s="1" t="inlineStr">
         <is>
-          <t>概念；线索</t>
+          <t>预感；概念；大致了解〈f.〉</t>
         </is>
       </c>
       <c r="E58" s="1" t="inlineStr">
@@ -3827,12 +3827,12 @@
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>[kankə] 机会〈n.f.〉</t>
+          <t>[ʃãːsə] 机会〈n.f.〉</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
         <is>
-          <t>kankə</t>
+          <t>ʃãːsə</t>
         </is>
       </c>
       <c r="D107" s="1" t="inlineStr">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>[zɛt͡sən] 坐下；放置〈v.〉</t>
+          <t>[zɛt͡sən] 放置；使坐下（sich setzen 坐下）〈v.〉</t>
         </is>
       </c>
       <c r="C130" s="1" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="D130" s="1" t="inlineStr">
         <is>
-          <t>坐下；放置</t>
+          <t>放置；使坐下（sich setzen 坐下）</t>
         </is>
       </c>
       <c r="E130" s="1" t="inlineStr">
@@ -7475,12 +7475,12 @@
       </c>
       <c r="B221" s="1" t="inlineStr">
         <is>
-          <t>[maɪnʊnk] 意见〈n.f.〉</t>
+          <t>[maɪnʊŋ] 意见〈n.f.〉</t>
         </is>
       </c>
       <c r="C221" s="1" t="inlineStr">
         <is>
-          <t>maɪnʊnk</t>
+          <t>maɪnʊŋ</t>
         </is>
       </c>
       <c r="D221" s="1" t="inlineStr">
@@ -9203,12 +9203,12 @@
       </c>
       <c r="B275" s="1" t="inlineStr">
         <is>
-          <t>[bɛvəɡʊnk] 运动；动作〈n.f.〉</t>
+          <t>[bɛvəɡʊŋ] 运动；动作〈n.f.〉</t>
         </is>
       </c>
       <c r="C275" s="1" t="inlineStr">
         <is>
-          <t>bɛvəɡʊnk</t>
+          <t>bɛvəɡʊŋ</t>
         </is>
       </c>
       <c r="D275" s="1" t="inlineStr">
@@ -12787,12 +12787,12 @@
       </c>
       <c r="B387" s="1" t="inlineStr">
         <is>
-          <t>[ʁeːɡiːʁʊnk] 政府〈n.f.〉</t>
+          <t>[ʁeːɡiːʁʊŋ] 政府〈n.f.〉</t>
         </is>
       </c>
       <c r="C387" s="1" t="inlineStr">
         <is>
-          <t>ʁeːɡiːʁʊnk</t>
+          <t>ʁeːɡiːʁʊŋ</t>
         </is>
       </c>
       <c r="D387" s="1" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="B441" s="1" t="inlineStr">
         <is>
-          <t>[ziːtʊat͡sjoːn] 情况〈n.f.〉</t>
+          <t>[zɪtuat͡sjoːn] 情况〈n.f.〉</t>
         </is>
       </c>
       <c r="C441" s="1" t="inlineStr">
         <is>
-          <t>ziːtʊat͡sjoːn</t>
+          <t>zɪtuat͡sjoːn</t>
         </is>
       </c>
       <c r="D441" s="1" t="inlineStr">
@@ -14675,7 +14675,7 @@
       </c>
       <c r="B446" s="1" t="inlineStr">
         <is>
-          <t>[voːʁaʊf] 指什么〈adv.〉</t>
+          <t>[voːʁaʊf] 在什么之上；据此〈adv.〉</t>
         </is>
       </c>
       <c r="C446" s="1" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="D446" s="1" t="inlineStr">
         <is>
-          <t>指什么</t>
+          <t>在什么之上；据此</t>
         </is>
       </c>
       <c r="E446" s="1" t="inlineStr">
@@ -16627,7 +16627,7 @@
       </c>
       <c r="B507" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁnzeːən] 电视〈n.〉</t>
+          <t>[fɛʁnzeːən] 电视；看电视〈n.〉</t>
         </is>
       </c>
       <c r="C507" s="1" t="inlineStr">
@@ -16637,7 +16637,7 @@
       </c>
       <c r="D507" s="1" t="inlineStr">
         <is>
-          <t>电视</t>
+          <t>电视；看电视</t>
         </is>
       </c>
       <c r="E507" s="1" t="inlineStr">
@@ -17811,7 +17811,7 @@
       </c>
       <c r="B544" s="1" t="inlineStr">
         <is>
-          <t>[zeː] 湖〈n.f.〉</t>
+          <t>[zeː] 湖〈m.〉；（die See）海〈f.〉〈n.f.〉</t>
         </is>
       </c>
       <c r="C544" s="1" t="inlineStr">
@@ -17821,7 +17821,7 @@
       </c>
       <c r="D544" s="1" t="inlineStr">
         <is>
-          <t>湖</t>
+          <t>湖〈m.〉；（die See）海〈f.〉</t>
         </is>
       </c>
       <c r="E544" s="1" t="inlineStr">
@@ -24819,7 +24819,7 @@
       </c>
       <c r="B763" s="1" t="inlineStr">
         <is>
-          <t>[hɪnɡeːən] 过去〈v.〉</t>
+          <t>[hɪnɡeːən] 去那儿；前往〈v.〉〈v.〉</t>
         </is>
       </c>
       <c r="C763" s="1" t="inlineStr">
@@ -24829,7 +24829,7 @@
       </c>
       <c r="D763" s="1" t="inlineStr">
         <is>
-          <t>过去</t>
+          <t>去那儿；前往〈v.〉</t>
         </is>
       </c>
       <c r="E763" s="1" t="inlineStr">
@@ -31891,12 +31891,12 @@
       </c>
       <c r="B984" s="1" t="inlineStr">
         <is>
-          <t>[beːdɔʏtʊnk] 意义〈n.f.〉</t>
+          <t>[beːdɔʏtʊŋ] 意义〈n.f.〉</t>
         </is>
       </c>
       <c r="C984" s="1" t="inlineStr">
         <is>
-          <t>beːdɔʏtʊnk</t>
+          <t>beːdɔʏtʊŋ</t>
         </is>
       </c>
       <c r="D984" s="1" t="inlineStr">
@@ -34931,7 +34931,7 @@
       </c>
       <c r="B1079" s="1" t="inlineStr">
         <is>
-          <t>[fʁɛmdə] 陌生的〈adj.〉</t>
+          <t>[fʁɛmdə] 陌生的（形容词原形为 fremd；fremde 亦作名词，指陌生人/异乡）〈adj.〉</t>
         </is>
       </c>
       <c r="C1079" s="1" t="inlineStr">
@@ -34941,7 +34941,7 @@
       </c>
       <c r="D1079" s="1" t="inlineStr">
         <is>
-          <t>陌生的</t>
+          <t>陌生的（形容词原形为 fremd；fremde 亦作名词，指陌生人/异乡）</t>
         </is>
       </c>
       <c r="E1079" s="1" t="inlineStr">
@@ -36147,7 +36147,7 @@
       </c>
       <c r="B1117" s="1" t="inlineStr">
         <is>
-          <t>[ʃpɪnən] 发疯（口语）〈v.〉</t>
+          <t>[ʃpɪnən] 纺织；（口语）发疯；胡说〈v.〉</t>
         </is>
       </c>
       <c r="C1117" s="1" t="inlineStr">
@@ -36157,7 +36157,7 @@
       </c>
       <c r="D1117" s="1" t="inlineStr">
         <is>
-          <t>发疯（口语）</t>
+          <t>纺织；（口语）发疯；胡说</t>
         </is>
       </c>
       <c r="E1117" s="1" t="inlineStr">
@@ -37171,12 +37171,12 @@
       </c>
       <c r="B1149" s="1" t="inlineStr">
         <is>
-          <t>[zoːfiːl] 那么多；一样多〈adv.〉</t>
+          <t>[zoːviːl] 那么多；一样多〈adv.〉</t>
         </is>
       </c>
       <c r="C1149" s="1" t="inlineStr">
         <is>
-          <t>zoːfiːl</t>
+          <t>zoːviːl</t>
         </is>
       </c>
       <c r="D1149" s="1" t="inlineStr">
@@ -38867,12 +38867,12 @@
       </c>
       <c r="B1202" s="1" t="inlineStr">
         <is>
-          <t>[kɪaɔ] 再见（口语）〈interj.〉</t>
+          <t>[tʃao] 再见（口语）〈interj.〉</t>
         </is>
       </c>
       <c r="C1202" s="1" t="inlineStr">
         <is>
-          <t>kɪaɔ</t>
+          <t>tʃao</t>
         </is>
       </c>
       <c r="D1202" s="1" t="inlineStr">
@@ -39443,12 +39443,12 @@
       </c>
       <c r="B1220" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁtaɪdɪɡʊnk] 防御〈n.f.〉</t>
+          <t>[fɛʁtaɪdɪɡʊŋ] 防御〈n.f.〉</t>
         </is>
       </c>
       <c r="C1220" s="1" t="inlineStr">
         <is>
-          <t>fɛʁtaɪdɪɡʊnk</t>
+          <t>fɛʁtaɪdɪɡʊŋ</t>
         </is>
       </c>
       <c r="D1220" s="1" t="inlineStr">
@@ -39571,12 +39571,12 @@
       </c>
       <c r="B1224" s="1" t="inlineStr">
         <is>
-          <t>[beːandlʊnk] 治疗〈n.f.〉</t>
+          <t>[beːandlʊŋ] 治疗〈n.f.〉</t>
         </is>
       </c>
       <c r="C1224" s="1" t="inlineStr">
         <is>
-          <t>beːandlʊnk</t>
+          <t>beːandlʊŋ</t>
         </is>
       </c>
       <c r="D1224" s="1" t="inlineStr">
@@ -41523,12 +41523,12 @@
       </c>
       <c r="B1285" s="1" t="inlineStr">
         <is>
-          <t>[ɡɔʊfəʁnɔʏɐ] 州长〈n.m.〉</t>
+          <t>[ɡuvɛʁnøːɐ] 州长〈n.m.〉</t>
         </is>
       </c>
       <c r="C1285" s="1" t="inlineStr">
         <is>
-          <t>ɡɔʊfəʁnɔʏɐ</t>
+          <t>ɡuvɛʁnøːɐ</t>
         </is>
       </c>
       <c r="D1285" s="1" t="inlineStr">
@@ -41747,12 +41747,12 @@
       </c>
       <c r="B1292" s="1" t="inlineStr">
         <is>
-          <t>[ʃtøːʁʊnk] 打扰；故障〈n.f.〉</t>
+          <t>[ʃtøːʁʊŋ] 打扰；故障〈n.f.〉</t>
         </is>
       </c>
       <c r="C1292" s="1" t="inlineStr">
         <is>
-          <t>ʃtøːʁʊnk</t>
+          <t>ʃtøːʁʊŋ</t>
         </is>
       </c>
       <c r="D1292" s="1" t="inlineStr">
@@ -44915,12 +44915,12 @@
       </c>
       <c r="B1391" s="1" t="inlineStr">
         <is>
-          <t>[ʃtɛlʊnk] 位置；姿态〈n.f.〉</t>
+          <t>[ʃtɛlʊŋ] 位置；姿态〈n.f.〉</t>
         </is>
       </c>
       <c r="C1391" s="1" t="inlineStr">
         <is>
-          <t>ʃtɛlʊnk</t>
+          <t>ʃtɛlʊŋ</t>
         </is>
       </c>
       <c r="D1391" s="1" t="inlineStr">
@@ -45907,12 +45907,12 @@
       </c>
       <c r="B1422" s="1" t="inlineStr">
         <is>
-          <t>[beːdɪnɡʊnk] 条件〈n.f.〉</t>
+          <t>[beːdɪnɡʊŋ] 条件〈n.f.〉</t>
         </is>
       </c>
       <c r="C1422" s="1" t="inlineStr">
         <is>
-          <t>beːdɪnɡʊnk</t>
+          <t>beːdɪnɡʊŋ</t>
         </is>
       </c>
       <c r="D1422" s="1" t="inlineStr">
@@ -49235,12 +49235,12 @@
       </c>
       <c r="B1526" s="1" t="inlineStr">
         <is>
-          <t>[pʁyːfʊnk] 考试〈n.f.〉</t>
+          <t>[pʁyːfʊŋ] 考试〈n.f.〉</t>
         </is>
       </c>
       <c r="C1526" s="1" t="inlineStr">
         <is>
-          <t>pʁyːfʊnk</t>
+          <t>pʁyːfʊŋ</t>
         </is>
       </c>
       <c r="D1526" s="1" t="inlineStr">
@@ -50291,12 +50291,12 @@
       </c>
       <c r="B1559" s="1" t="inlineStr">
         <is>
-          <t>[aɪnstəlʊnk] 态度；设置〈n.f.〉</t>
+          <t>[aɪnstəlʊŋ] 态度；设置〈n.f.〉</t>
         </is>
       </c>
       <c r="C1559" s="1" t="inlineStr">
         <is>
-          <t>aɪnstəlʊnk</t>
+          <t>aɪnstəlʊŋ</t>
         </is>
       </c>
       <c r="D1559" s="1" t="inlineStr">
@@ -51315,12 +51315,12 @@
       </c>
       <c r="B1591" s="1" t="inlineStr">
         <is>
-          <t>[ʊmɡəbʊnk] 环境〈n.f.〉</t>
+          <t>[ʊmɡəbʊŋ] 环境〈n.f.〉</t>
         </is>
       </c>
       <c r="C1591" s="1" t="inlineStr">
         <is>
-          <t>ʊmɡəbʊnk</t>
+          <t>ʊmɡəbʊŋ</t>
         </is>
       </c>
       <c r="D1591" s="1" t="inlineStr">
@@ -51891,12 +51891,12 @@
       </c>
       <c r="B1609" s="1" t="inlineStr">
         <is>
-          <t>[liːfəʁʊnk] 送货〈n.f.〉</t>
+          <t>[liːfəʁʊŋ] 送货〈n.f.〉</t>
         </is>
       </c>
       <c r="C1609" s="1" t="inlineStr">
         <is>
-          <t>liːfəʁʊnk</t>
+          <t>liːfəʁʊŋ</t>
         </is>
       </c>
       <c r="D1609" s="1" t="inlineStr">
@@ -52435,12 +52435,12 @@
       </c>
       <c r="B1626" s="1" t="inlineStr">
         <is>
-          <t>[vɪʁkʊnk] 效果〈n.f.〉</t>
+          <t>[vɪʁkʊŋ] 效果〈n.f.〉</t>
         </is>
       </c>
       <c r="C1626" s="1" t="inlineStr">
         <is>
-          <t>vɪʁkʊnk</t>
+          <t>vɪʁkʊŋ</t>
         </is>
       </c>
       <c r="D1626" s="1" t="inlineStr">
@@ -54035,7 +54035,7 @@
       </c>
       <c r="B1676" s="1" t="inlineStr">
         <is>
-          <t>[ʃtɔʏɐ] 税；方向盘〈n.f.〉</t>
+          <t>[ʃtɔʏɐ] 税〈n.f.〉；（das Steuer）舵；方向盘〈n.n.〉〈n.f.〉</t>
         </is>
       </c>
       <c r="C1676" s="1" t="inlineStr">
@@ -54045,7 +54045,7 @@
       </c>
       <c r="D1676" s="1" t="inlineStr">
         <is>
-          <t>税；方向盘</t>
+          <t>税〈n.f.〉；（das Steuer）舵；方向盘〈n.n.〉</t>
         </is>
       </c>
       <c r="E1676" s="1" t="inlineStr">
@@ -54547,12 +54547,12 @@
       </c>
       <c r="B1692" s="1" t="inlineStr">
         <is>
-          <t>[ʁɛtʊnk] 营救〈n.f.〉</t>
+          <t>[ʁɛtʊŋ] 营救〈n.f.〉</t>
         </is>
       </c>
       <c r="C1692" s="1" t="inlineStr">
         <is>
-          <t>ʁɛtʊnk</t>
+          <t>ʁɛtʊŋ</t>
         </is>
       </c>
       <c r="D1692" s="1" t="inlineStr">
@@ -56051,12 +56051,12 @@
       </c>
       <c r="B1739" s="1" t="inlineStr">
         <is>
-          <t>[zɪt͡sʊnk] 会议〈n.f.〉</t>
+          <t>[zɪt͡sʊŋ] 会议〈n.f.〉</t>
         </is>
       </c>
       <c r="C1739" s="1" t="inlineStr">
         <is>
-          <t>zɪt͡sʊnk</t>
+          <t>zɪt͡sʊŋ</t>
         </is>
       </c>
       <c r="D1739" s="1" t="inlineStr">
@@ -58067,12 +58067,12 @@
       </c>
       <c r="B1802" s="1" t="inlineStr">
         <is>
-          <t>[aʊfʁəɡʊnk] 激动〈n.f.〉</t>
+          <t>[aʊfʁəɡʊŋ] 激动〈n.f.〉</t>
         </is>
       </c>
       <c r="C1802" s="1" t="inlineStr">
         <is>
-          <t>aʊfʁəɡʊnk</t>
+          <t>aʊfʁəɡʊŋ</t>
         </is>
       </c>
       <c r="D1802" s="1" t="inlineStr">
@@ -59891,12 +59891,12 @@
       </c>
       <c r="B1859" s="1" t="inlineStr">
         <is>
-          <t>[vhɪskɛʏ] 威士忌〈n.m.〉</t>
+          <t>[vɪskɛʏ] 威士忌〈n.m.〉</t>
         </is>
       </c>
       <c r="C1859" s="1" t="inlineStr">
         <is>
-          <t>vhɪskɛʏ</t>
+          <t>vɪskɛʏ</t>
         </is>
       </c>
       <c r="D1859" s="1" t="inlineStr">
@@ -61523,12 +61523,12 @@
       </c>
       <c r="B1910" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁlət͡sʊnk] 伤害〈n.f.〉</t>
+          <t>[fɛʁlət͡sʊŋ] 伤害〈n.f.〉</t>
         </is>
       </c>
       <c r="C1910" s="1" t="inlineStr">
         <is>
-          <t>fɛʁlət͡sʊnk</t>
+          <t>fɛʁlət͡sʊŋ</t>
         </is>
       </c>
       <c r="D1910" s="1" t="inlineStr">
@@ -62003,12 +62003,12 @@
       </c>
       <c r="B1925" s="1" t="inlineStr">
         <is>
-          <t>[ɛntfəʁnʊnk] 距离〈n.f.〉</t>
+          <t>[ɛntfəʁnʊŋ] 距离〈n.f.〉</t>
         </is>
       </c>
       <c r="C1925" s="1" t="inlineStr">
         <is>
-          <t>ɛntfəʁnʊnk</t>
+          <t>ɛntfəʁnʊŋ</t>
         </is>
       </c>
       <c r="D1925" s="1" t="inlineStr">
@@ -63667,12 +63667,12 @@
       </c>
       <c r="B1977" s="1" t="inlineStr">
         <is>
-          <t>[kɔvbɔʏ] 牛仔〈n.m.〉</t>
+          <t>[kaʊbɔɪ] 牛仔〈n.m.〉</t>
         </is>
       </c>
       <c r="C1977" s="1" t="inlineStr">
         <is>
-          <t>kɔvbɔʏ</t>
+          <t>kaʊbɔɪ</t>
         </is>
       </c>
       <c r="D1977" s="1" t="inlineStr">
@@ -65523,7 +65523,7 @@
       </c>
       <c r="B2035" s="1" t="inlineStr">
         <is>
-          <t>[miːnə] 矿井〈n.f.〉</t>
+          <t>[miːnə] 矿井；地雷；矿〈n.f.〉</t>
         </is>
       </c>
       <c r="C2035" s="1" t="inlineStr">
@@ -65533,7 +65533,7 @@
       </c>
       <c r="D2035" s="1" t="inlineStr">
         <is>
-          <t>矿井</t>
+          <t>矿井；地雷；矿</t>
         </is>
       </c>
       <c r="E2035" s="1" t="inlineStr">
@@ -68339,12 +68339,12 @@
       </c>
       <c r="B2123" s="1" t="inlineStr">
         <is>
-          <t>[tʁɛnʊnk] 分离〈n.f.〉</t>
+          <t>[tʁɛnʊŋ] 分离〈n.f.〉</t>
         </is>
       </c>
       <c r="C2123" s="1" t="inlineStr">
         <is>
-          <t>tʁɛnʊnk</t>
+          <t>tʁɛnʊŋ</t>
         </is>
       </c>
       <c r="D2123" s="1" t="inlineStr">
@@ -68563,12 +68563,12 @@
       </c>
       <c r="B2130" s="1" t="inlineStr">
         <is>
-          <t>[tiːmɪnk] 时机〈n.〉</t>
+          <t>[tiːmɪŋ] 时机〈n.〉</t>
         </is>
       </c>
       <c r="C2130" s="1" t="inlineStr">
         <is>
-          <t>tiːmɪnk</t>
+          <t>tiːmɪŋ</t>
         </is>
       </c>
       <c r="D2130" s="1" t="inlineStr">
@@ -70995,12 +70995,12 @@
       </c>
       <c r="B2206" s="1" t="inlineStr">
         <is>
-          <t>[ɛntaltən] 包含〈v.〉</t>
+          <t>[ɛnthaltən] 包含〈v.〉</t>
         </is>
       </c>
       <c r="C2206" s="1" t="inlineStr">
         <is>
-          <t>ɛntaltən</t>
+          <t>ɛnthaltən</t>
         </is>
       </c>
       <c r="D2206" s="1" t="inlineStr">
@@ -73811,7 +73811,7 @@
       </c>
       <c r="B2294" s="1" t="inlineStr">
         <is>
-          <t>[ɛʁɡɐn] 生气〈v.〉</t>
+          <t>[ɛʁɡɐn] 使恼怒；惹人生气〈v.〉〈v.〉</t>
         </is>
       </c>
       <c r="C2294" s="1" t="inlineStr">
@@ -73821,7 +73821,7 @@
       </c>
       <c r="D2294" s="1" t="inlineStr">
         <is>
-          <t>生气</t>
+          <t>使恼怒；惹人生气〈v.〉</t>
         </is>
       </c>
       <c r="E2294" s="1" t="inlineStr">
@@ -74163,12 +74163,12 @@
       </c>
       <c r="B2305" s="1" t="inlineStr">
         <is>
-          <t>[ʁeːzəʁfiːʁt] 预定的；矜持〈adj.〉</t>
+          <t>[ʁezɛʁviːʁt] 预定的；矜持〈adj.〉</t>
         </is>
       </c>
       <c r="C2305" s="1" t="inlineStr">
         <is>
-          <t>ʁeːzəʁfiːʁt</t>
+          <t>ʁezɛʁviːʁt</t>
         </is>
       </c>
       <c r="D2305" s="1" t="inlineStr">
@@ -75219,12 +75219,12 @@
       </c>
       <c r="B2338" s="1" t="inlineStr">
         <is>
-          <t>[hɔʏptlɪnk] 首领〈n.m.〉</t>
+          <t>[hɔʏptlɪŋ] 首领〈n.m.〉</t>
         </is>
       </c>
       <c r="C2338" s="1" t="inlineStr">
         <is>
-          <t>hɔʏptlɪnk</t>
+          <t>hɔʏptlɪŋ</t>
         </is>
       </c>
       <c r="D2338" s="1" t="inlineStr">
@@ -77779,7 +77779,7 @@
       </c>
       <c r="B2418" s="1" t="inlineStr">
         <is>
-          <t>[ʁeːɡəln] 规则〈n.f.〉</t>
+          <t>[ʁeːɡəln] 调节；规定〈n.f.〉</t>
         </is>
       </c>
       <c r="C2418" s="1" t="inlineStr">
@@ -77789,7 +77789,7 @@
       </c>
       <c r="D2418" s="1" t="inlineStr">
         <is>
-          <t>规则</t>
+          <t>调节；规定</t>
         </is>
       </c>
       <c r="E2418" s="1" t="inlineStr">
@@ -77811,7 +77811,7 @@
       </c>
       <c r="B2419" s="1" t="inlineStr">
         <is>
-          <t>[anɡəzɪçt] 面临〈n.〉</t>
+          <t>[anɡəzɪçt] 脸；面孔；面容〈n.〉</t>
         </is>
       </c>
       <c r="C2419" s="1" t="inlineStr">
@@ -77821,7 +77821,7 @@
       </c>
       <c r="D2419" s="1" t="inlineStr">
         <is>
-          <t>面临</t>
+          <t>脸；面孔；面容</t>
         </is>
       </c>
       <c r="E2419" s="1" t="inlineStr">
@@ -78131,12 +78131,12 @@
       </c>
       <c r="B2429" s="1" t="inlineStr">
         <is>
-          <t>[diːfɪzɪoːn] 师；部门〈n.f.〉</t>
+          <t>[divizi̯oːn] 师；部门〈n.f.〉</t>
         </is>
       </c>
       <c r="C2429" s="1" t="inlineStr">
         <is>
-          <t>diːfɪzɪoːn</t>
+          <t>divizi̯oːn</t>
         </is>
       </c>
       <c r="D2429" s="1" t="inlineStr">
@@ -79155,12 +79155,12 @@
       </c>
       <c r="B2461" s="1" t="inlineStr">
         <is>
-          <t>[haltʊnk] 姿态；态度〈n.f.〉</t>
+          <t>[haltʊŋ] 姿态；态度〈n.f.〉</t>
         </is>
       </c>
       <c r="C2461" s="1" t="inlineStr">
         <is>
-          <t>haltʊnk</t>
+          <t>haltʊŋ</t>
         </is>
       </c>
       <c r="D2461" s="1" t="inlineStr">
@@ -83219,7 +83219,7 @@
       </c>
       <c r="B2588" s="1" t="inlineStr">
         <is>
-          <t>[kamɐ] 房间〈n.f.〉</t>
+          <t>[kamɐ] 室；腔；议院〈n.f.〉〈n.f.〉</t>
         </is>
       </c>
       <c r="C2588" s="1" t="inlineStr">
@@ -83229,7 +83229,7 @@
       </c>
       <c r="D2588" s="1" t="inlineStr">
         <is>
-          <t>房间</t>
+          <t>室；腔；议院〈n.f.〉</t>
         </is>
       </c>
       <c r="E2588" s="1" t="inlineStr">
@@ -83955,12 +83955,12 @@
       </c>
       <c r="B2611" s="1" t="inlineStr">
         <is>
-          <t>[bɛɡlaɪtʊnk] 陪同〈n.f.〉</t>
+          <t>[bɛɡlaɪtʊŋ] 陪同〈n.f.〉</t>
         </is>
       </c>
       <c r="C2611" s="1" t="inlineStr">
         <is>
-          <t>bɛɡlaɪtʊnk</t>
+          <t>bɛɡlaɪtʊŋ</t>
         </is>
       </c>
       <c r="D2611" s="1" t="inlineStr">
@@ -85971,12 +85971,12 @@
       </c>
       <c r="B2674" s="1" t="inlineStr">
         <is>
-          <t>[ʃpanʊnk] 紧张；电压〈n.f.〉</t>
+          <t>[ʃpanʊŋ] 紧张；电压〈n.f.〉</t>
         </is>
       </c>
       <c r="C2674" s="1" t="inlineStr">
         <is>
-          <t>ʃpanʊnk</t>
+          <t>ʃpanʊŋ</t>
         </is>
       </c>
       <c r="D2674" s="1" t="inlineStr">
@@ -86003,12 +86003,12 @@
       </c>
       <c r="B2675" s="1" t="inlineStr">
         <is>
-          <t>[bɛstɪmʊnk] 命运；规定〈n.f.〉</t>
+          <t>[bɛstɪmʊŋ] 命运；规定〈n.f.〉</t>
         </is>
       </c>
       <c r="C2675" s="1" t="inlineStr">
         <is>
-          <t>bɛstɪmʊnk</t>
+          <t>bɛstɪmʊŋ</t>
         </is>
       </c>
       <c r="D2675" s="1" t="inlineStr">
@@ -86995,12 +86995,12 @@
       </c>
       <c r="B2706" s="1" t="inlineStr">
         <is>
-          <t>[aːnəʁkənʊnk] 认可〈n.f.〉</t>
+          <t>[aːnəʁkənʊŋ] 认可〈n.f.〉</t>
         </is>
       </c>
       <c r="C2706" s="1" t="inlineStr">
         <is>
-          <t>aːnəʁkənʊnk</t>
+          <t>aːnəʁkənʊŋ</t>
         </is>
       </c>
       <c r="D2706" s="1" t="inlineStr">
@@ -87251,12 +87251,12 @@
       </c>
       <c r="B2714" s="1" t="inlineStr">
         <is>
-          <t>[bɛstɛtɪɡʊnk] 确认〈n.f.〉</t>
+          <t>[bɛstɛtɪɡʊŋ] 确认〈n.f.〉</t>
         </is>
       </c>
       <c r="C2714" s="1" t="inlineStr">
         <is>
-          <t>bɛstɛtɪɡʊnk</t>
+          <t>bɛstɛtɪɡʊŋ</t>
         </is>
       </c>
       <c r="D2714" s="1" t="inlineStr">
@@ -88307,7 +88307,7 @@
       </c>
       <c r="B2747" s="1" t="inlineStr">
         <is>
-          <t>[aʊsvəndɪç] 背诵地〈adv.〉</t>
+          <t>[aʊsvəndɪç] 凭记忆地；熟记地（如 auswendig lernen 背熟）〈adv.〉</t>
         </is>
       </c>
       <c r="C2747" s="1" t="inlineStr">
@@ -88317,7 +88317,7 @@
       </c>
       <c r="D2747" s="1" t="inlineStr">
         <is>
-          <t>背诵地</t>
+          <t>凭记忆地；熟记地（如 auswendig lernen 背熟）</t>
         </is>
       </c>
       <c r="E2747" s="1" t="inlineStr">
@@ -88467,12 +88467,12 @@
       </c>
       <c r="B2752" s="1" t="inlineStr">
         <is>
-          <t>[bluːtʊnk] 出血〈n.f.〉</t>
+          <t>[bluːtʊŋ] 出血〈n.f.〉</t>
         </is>
       </c>
       <c r="C2752" s="1" t="inlineStr">
         <is>
-          <t>bluːtʊnk</t>
+          <t>bluːtʊŋ</t>
         </is>
       </c>
       <c r="D2752" s="1" t="inlineStr">
@@ -88947,12 +88947,12 @@
       </c>
       <c r="B2767" s="1" t="inlineStr">
         <is>
-          <t>[ɛntdəkʊnk] 发现〈n.f.〉</t>
+          <t>[ɛntdəkʊŋ] 发现〈n.f.〉</t>
         </is>
       </c>
       <c r="C2767" s="1" t="inlineStr">
         <is>
-          <t>ɛntdəkʊnk</t>
+          <t>ɛntdəkʊŋ</t>
         </is>
       </c>
       <c r="D2767" s="1" t="inlineStr">
